--- a/questionnaire_templates/020_new_graduate_nurse_interview_questionnaire--questionnaire_templates.xlsx
+++ b/questionnaire_templates/020_new_graduate_nurse_interview_questionnaire--questionnaire_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -823,8 +823,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -852,12 +852,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'high_school',_'value':_1}</t>
+          <t>high_school</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'High School', 'value': 1}</t>
+          <t>High School</t>
         </is>
       </c>
     </row>
@@ -869,12 +869,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'diploma',_'value':_2}</t>
+          <t>diploma</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Diploma', 'value': 2}</t>
+          <t>Diploma</t>
         </is>
       </c>
     </row>
@@ -886,12 +886,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_"associate's",_'value':_3}</t>
+          <t>associate's</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': "Associate's", 'value': 3}</t>
+          <t>Associate's</t>
         </is>
       </c>
     </row>
@@ -903,12 +903,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_"bachelor's",_'value':_4}</t>
+          <t>bachelor's</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': "Bachelor's", 'value': 4}</t>
+          <t>Bachelor's</t>
         </is>
       </c>
     </row>
@@ -920,12 +920,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_"master's",_'value':_5}</t>
+          <t>master's</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': "Master's", 'value': 5}</t>
+          <t>Master's</t>
         </is>
       </c>
     </row>
@@ -937,12 +937,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'doctorate',_'value':_6}</t>
+          <t>doctorate</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Doctorate', 'value': 6}</t>
+          <t>Doctorate</t>
         </is>
       </c>
     </row>
@@ -954,12 +954,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'active_and_current',_'value':_1}</t>
+          <t>active_and_current</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Active and Current', 'value': 1}</t>
+          <t>Active and Current</t>
         </is>
       </c>
     </row>
@@ -971,12 +971,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'active_and_expired',_'value':_2}</t>
+          <t>active_and_expired</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Active and Expired', 'value': 2}</t>
+          <t>Active and Expired</t>
         </is>
       </c>
     </row>
@@ -988,12 +988,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'inactive',_'value':_3}</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Inactive', 'value': 3}</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
@@ -1005,12 +1005,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'bls_(basic_life_support)',_'value':_1}</t>
+          <t>bls_(basic_life_support)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'BLS (Basic Life Support)', 'value': 1}</t>
+          <t>BLS (Basic Life Support)</t>
         </is>
       </c>
     </row>
@@ -1022,12 +1022,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'acls_(advanced_life_support)',_'value':_2}</t>
+          <t>acls_(advanced_life_support)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'ACLS (Advanced Life Support)', 'value': 2}</t>
+          <t>ACLS (Advanced Life Support)</t>
         </is>
       </c>
     </row>
@@ -1039,12 +1039,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'pals_(pediatric_advanced_life_support)',_'value':_3}</t>
+          <t>pals_(pediatric_advanced_life_support)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'PALS (Pediatric Advanced Life Support)', 'value': 3}</t>
+          <t>PALS (Pediatric Advanced Life Support)</t>
         </is>
       </c>
     </row>
@@ -1056,12 +1056,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'none',_'value':_4}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'None', 'value': 4}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'leadership',_'value':_1}</t>
+          <t>leadership</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Leadership', 'value': 1}</t>
+          <t>Leadership</t>
         </is>
       </c>
     </row>
@@ -1090,12 +1090,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'communication',_'value':_2}</t>
+          <t>communication</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Communication', 'value': 2}</t>
+          <t>Communication</t>
         </is>
       </c>
     </row>
@@ -1107,12 +1107,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'time_management',_'value':_3}</t>
+          <t>time_management</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Time Management', 'value': 3}</t>
+          <t>Time Management</t>
         </is>
       </c>
     </row>
@@ -1124,12 +1124,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'none',_'value':_4}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'None', 'value': 4}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1141,12 +1141,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'basic_life_support',_'value':_1}</t>
+          <t>basic_life_support</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Basic Life Support', 'value': 1}</t>
+          <t>Basic Life Support</t>
         </is>
       </c>
     </row>
@@ -1158,12 +1158,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'iv_therapy',_'value':_2}</t>
+          <t>iv_therapy</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'IV Therapy', 'value': 2}</t>
+          <t>IV Therapy</t>
         </is>
       </c>
     </row>
@@ -1175,12 +1175,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'medication_management',_'value':_3}</t>
+          <t>medication_management</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Medication Management', 'value': 3}</t>
+          <t>Medication Management</t>
         </is>
       </c>
     </row>
@@ -1192,12 +1192,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'none',_'value':_4}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'None', 'value': 4}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1209,12 +1209,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'communication',_'value':_1}</t>
+          <t>communication</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Communication', 'value': 1}</t>
+          <t>Communication</t>
         </is>
       </c>
     </row>
@@ -1226,12 +1226,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'time_management',_'value':_2}</t>
+          <t>time_management</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Time Management', 'value': 2}</t>
+          <t>Time Management</t>
         </is>
       </c>
     </row>
@@ -1243,12 +1243,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'leadership',_'value':_3}</t>
+          <t>leadership</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Leadership', 'value': 3}</t>
+          <t>Leadership</t>
         </is>
       </c>
     </row>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'problem_solving',_'value':_4}</t>
+          <t>problem_solving</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Problem Solving', 'value': 4}</t>
+          <t>Problem Solving</t>
         </is>
       </c>
     </row>
@@ -1277,12 +1277,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'none',_'value':_5}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'None', 'value': 5}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
